--- a/tasks/finalpool/sf-hr-satisfaction-analysis/groundtruth_workspace/HR_Satisfaction_Report.xlsx
+++ b/tasks/finalpool/sf-hr-satisfaction-analysis/groundtruth_workspace/HR_Satisfaction_Report.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,27 +418,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Avg_Satisfaction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Avg_Work_Life_Balance</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Avg_Rating</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Employees</t>
         </is>
@@ -451,39 +447,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>6.59</v>
       </c>
       <c r="C2" t="n">
-        <v>4.49</v>
+        <v>4.54</v>
       </c>
       <c r="D2" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="E2" t="n">
-        <v>7232</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>6.59</v>
       </c>
       <c r="C3" t="n">
-        <v>4.54</v>
+        <v>4.49</v>
       </c>
       <c r="D3" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="E3" t="n">
-        <v>7148</v>
+        <v>7232</v>
       </c>
     </row>
     <row r="4">
@@ -596,12 +592,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -635,7 +631,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
